--- a/tests/testthat/fixtures/ref-kreise-testfixture-jaehrlich.xlsx
+++ b/tests/testthat/fixtures/ref-kreise-testfixture-jaehrlich.xlsx
@@ -18,34 +18,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
   <si>
-    <t>KOPF1</t>
-  </si>
-  <si>
-    <t>KOPF2</t>
-  </si>
-  <si>
-    <t>KOPF3</t>
-  </si>
-  <si>
-    <t>KOPF4</t>
-  </si>
-  <si>
-    <t>KOPF5</t>
-  </si>
-  <si>
-    <t>KOPF6</t>
-  </si>
-  <si>
-    <t>KOPF7</t>
-  </si>
-  <si>
-    <t>KOPF8</t>
+    <t>HEAD1</t>
+  </si>
+  <si>
+    <t>HEAD2</t>
+  </si>
+  <si>
+    <t>HEAD3</t>
+  </si>
+  <si>
+    <t>HEAD4</t>
+  </si>
+  <si>
+    <t>HEAD5</t>
+  </si>
+  <si>
+    <t>HEAD6</t>
+  </si>
+  <si>
+    <t>HEAD7</t>
+  </si>
+  <si>
+    <t>HEAD8</t>
   </si>
   <si>
     <t>01000001</t>
   </si>
   <si>
-    <t>Kreis A</t>
+    <t>District A</t>
   </si>
   <si>
     <t>1</t>
@@ -60,7 +60,7 @@
     <t>01000002</t>
   </si>
   <si>
-    <t>Kreis B</t>
+    <t>District B</t>
   </si>
   <si>
     <t>0.4</t>
@@ -78,7 +78,7 @@
     <t>01000009</t>
   </si>
   <si>
-    <t>Kreis N</t>
+    <t>District N</t>
   </si>
   <si>
     <t>0.6</t>
@@ -96,13 +96,13 @@
     <t>01000010</t>
   </si>
   <si>
-    <t>Kreis M</t>
-  </si>
-  <si>
-    <t>KOPF9</t>
-  </si>
-  <si>
-    <t>KOPF10</t>
+    <t>District M</t>
+  </si>
+  <si>
+    <t>HEAD9</t>
+  </si>
+  <si>
+    <t>HEAD10</t>
   </si>
   <si>
     <t>10</t>
